--- a/Formulario.xlsx
+++ b/Formulario.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universalleafcorp-my.sharepoint.com/personal/secretd1_universalleaf_com/Documents/APT/Área de Trabalho/TesteFormulário/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universalleafcorp-my.sharepoint.com/personal/secretd1_universalleaf_com/Documents/APT/Área de Trabalho/Formulário/Projeto_Teste/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_F25DC773A252ABDACC1048F1D11C4B9C5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C7A041A-898B-460D-A20F-94855C7D5302}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC1048F1D11C4B9C5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E016EF33-2488-4045-8893-90C354C96944}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,23 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
-  <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>Idade</t>
-  </si>
-  <si>
-    <t>Cidade</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>Possui Crea Ativo</t>
   </si>
   <si>
-    <t>Numero CREA</t>
-  </si>
-  <si>
     <t>pergunta</t>
   </si>
   <si>
@@ -81,7 +69,25 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Telefone</t>
+    <t>Nome Completo:</t>
+  </si>
+  <si>
+    <t>Idade:</t>
+  </si>
+  <si>
+    <t>Cidade:</t>
+  </si>
+  <si>
+    <t>Telefone:</t>
+  </si>
+  <si>
+    <t>E-mail:</t>
+  </si>
+  <si>
+    <t>Possui Crea Ativo?</t>
+  </si>
+  <si>
+    <t>Número CREA:</t>
   </si>
 </sst>
 </file>
@@ -399,10 +405,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
@@ -412,77 +418,74 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -490,19 +493,33 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Formulario.xlsx
+++ b/Formulario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universalleafcorp-my.sharepoint.com/personal/secretd1_universalleaf_com/Documents/APT/Área de Trabalho/Formulário/Projeto_Teste/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC1048F1D11C4B9C5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E016EF33-2488-4045-8893-90C354C96944}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_F25DC773A252ABDACC1048F1D11C4B9C5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D3F06D8-2505-48AB-A684-E956B841004C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
-  <si>
-    <t>Possui Crea Ativo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>pergunta</t>
   </si>
@@ -408,118 +405,118 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
